--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5605.05</v>
+        <v>5474.63</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>37692.53</v>
+        <v>37849.18</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1213.96</v>
+        <v>1216.48</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12526.21</v>
+        <v>12619.53</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>40831.61</v>
+        <v>40387.43</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36514.69</v>
+        <v>36943.03</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>77.48999999999999</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1660.42</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>31880.12</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6874.55</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8571.700000000001</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25715.11</v>
+        <v>25584.85</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>37586.6</v>
+        <v>37396.2</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>19205.77</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,68 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>18153.11</v>
+        <v>18116.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2852-777-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>6558.98</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2852-777-CM26</t>
+          <t>934-114-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,373 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
+        <v>2594.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1860-62-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>8202.01</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2852-777-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
         <v>6558.98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>934-131-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>2960.53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>934-134-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>3942.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>934-136-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.659.446-6</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>878.41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1057539-4659-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>62192.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>934-81-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>75.89</v>
+        <v>1548.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1626.3</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>31224.93</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6939.85</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.735.787-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8605.07</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057536-1747-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25584.85</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057536-1856-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>37396.2</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>1057536-1747-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>19108.48</v>
+        <v>25584.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>1057536-1856-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>18116.72</v>
+        <v>37396.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>934-114-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2594.9</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1860-62-CM26</t>
+          <t>934-114-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8202.01</v>
+        <v>2594.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2852-777-CM26</t>
+          <t>1860-62-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6558.98</v>
+        <v>8202.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>934-131-CM26</t>
+          <t>2852-777-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2960.53</v>
+        <v>6558.98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>934-131-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3942.4</v>
+        <v>2960.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>934-136-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.659.446-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>878.41</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057539-4659-CM26</t>
+          <t>934-136-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>77.659.446-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,7 +1850,190 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
+        <v>878.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1057539-4659-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>62192.68</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1664-616-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.602.271-7</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>VIVANET</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>6287.49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1057532-1385-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>7476.08</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +997,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1063,7 +1079,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>4215-18-SE26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1104,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,28 +1119,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>31224.93</v>
+        <v>84491.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1154,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1164,12 +1184,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1199,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6939.85</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1220,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,28 +1245,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.735.787-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8605.07</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1285,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1295,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,22 +1310,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>19108.48</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="15">
@@ -1429,7 +1457,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1472,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1482,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1497,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>18116.72</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>934-114-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1532,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1538,20 +1570,24 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2594.9</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1860-62-CM26</t>
+          <t>934-114-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1602,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1612,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,28 +1627,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8202.01</v>
+        <v>2594.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2852-777-CM26</t>
+          <t>1860-62-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1672,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1692,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1707,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6558.98</v>
+        <v>8202.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>934-131-CM26</t>
+          <t>2852-777-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1728,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1738,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1753,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1768,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2960.53</v>
+        <v>6558.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>934-131-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,12 +1789,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1782,20 +1822,24 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3942.4</v>
+        <v>2960.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>934-136-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,12 +1854,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1835,28 +1879,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.659.446-6</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>878.41</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057539-4659-CM26</t>
+          <t>934-136-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1919,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,28 +1944,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.659.446-6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>62192.68</v>
+        <v>878.41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1664-616-CM26</t>
+          <t>1057539-4659-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1979,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.602.271-7</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +2009,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6287.49</v>
+        <v>62192.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057532-1385-CM26</t>
+          <t>1664-616-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +2049,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.602.271-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2074,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,6 +2089,71 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
+        <v>6287.49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1057532-1385-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>7476.08</v>
       </c>
     </row>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,32 +989,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>75.89</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>4215-18-SE26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1034,17 +1030,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1073,13 +1069,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1626.3</v>
+        <v>84491.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4215-18-SE26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1138,13 +1134,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>84491.62</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,7 +1160,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1184,22 +1180,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31224.93</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="13">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2155,6 +2155,128 @@
       </c>
       <c r="M27" s="2" t="n">
         <v>7476.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>934-198-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>3565.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1057539-8780-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Javier Orlando</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.548.886-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>58788.95</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1010,7 +1010,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4215-18-SE26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>84491.62</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>75.89</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>4215-18-SE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1626.3</v>
+        <v>84491.62</v>
       </c>
     </row>
     <row r="13">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1969,7 +1969,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057539-4659-CM26</t>
+          <t>934-137-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>62192.68</v>
+        <v>5292.15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1664-616-CM26</t>
+          <t>1057539-4659-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.271-7</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2074,28 +2074,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6287.49</v>
+        <v>62192.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057532-1385-CM26</t>
+          <t>1664-616-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2110,22 +2114,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.602.271-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2135,32 +2139,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7476.08</v>
+        <v>6287.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>934-198-CM26</t>
+          <t>1057532-1385-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2200,28 +2200,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3565.43</v>
+        <v>7476.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057539-8780-CM26</t>
+          <t>934-198-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2236,7 +2240,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2246,12 +2250,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2261,12 +2265,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Javier Orlando</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.548.886-9</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2276,6 +2280,67 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
+        <v>3565.43</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1057539-8780-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Javier Orlando</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.548.886-9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>58788.95</v>
       </c>
     </row>
